--- a/outils/work/normalized.xlsx
+++ b/outils/work/normalized.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Les échos du passé</t>
+          <t>Urchin</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -504,17 +504,17 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mascha Schilinski</t>
+          <t>Harris Dickinson</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prix du jury Cannes 2025</t>
+          <t>Grand Prix Jury de jeunes Carbonne fait son cinéma - Meilleure interprétation Un certain regard Cannes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -523,133 +523,141 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Christy and his brother</t>
+          <t>Le sommet des dieux</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CM1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Brendan Canty</t>
-        </is>
-      </c>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Coip de cœur</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2,80 €</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Patrick Imbert / Collège Noé</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ma frère</t>
+          <t>Rue Malaga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lise Akoka, Romane Gueret</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Maryam Touzani</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Prix du public Venise</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Séance EPHAD HANDI - Famille</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Tarif Unique 5 €</t>
-        </is>
-      </c>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hamnet</t>
+          <t>Microcosmos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chloé Zhao</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Meilleure film dramatique et meilleure actrice Golden Globes 2026</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Claude Nuridsany, Marie Pérennou</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2,80 €</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Ec Labsstide Clermont</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Alter ego</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -660,18 +668,18 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Irene Iborra</t>
+          <t>Nicolas Charlet, Bruno Lavaine</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Séance EPHAD HANDI</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tarif Unique 4,50 €</t>
+          <t>Tarif Unique 5 €</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -679,57 +687,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bardot</t>
+          <t>La couleuvre noire</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Alain Berliner, Elora Thevenet</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Aurélien Vernhes-Lermusiaux</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prix Fondation Gan</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ciné Documentaire du samedi 18h</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Adhérents 4 € - Autres 5 €</t>
-        </is>
-      </c>
+          <t>Cinélatino Avant-première</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grand ciel</t>
+          <t>L'ourse et l'oiseau</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -740,28 +748,36 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akihiro Hata</t>
+          <t>Marie Caudry, Aurore Peuffier, Nina Bisyarina</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Tarif Unique 3 €</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Biscuit le chien fantastique</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -772,64 +788,80 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shea Wageman</t>
+          <t>Edouard Bergeon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Ciné Documentaire du samedi 18h</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>invité Jérôme Bayle attente de réponse</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L'affaire Bojarski</t>
+          <t>Marty Supreme</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jean-Paul Salomé</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+          <t>Josh Safdie</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Golden Globe meilleur acteur</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tafiti</t>
+          <t>Marsupilami</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -840,13 +872,13 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nina Wels</t>
+          <t>Philippe Lacheau</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Famille, Jeune Public</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -855,89 +887,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Le mage du Kremlin</t>
+          <t>Maigret et le mort amoureux</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olivier Assayas</t>
+          <t>Pascal Bonitzer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The mastermind</t>
+          <t>Les Tourouges et les Toubleus</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kelly Reichardt</t>
+          <t>Samantha Cutler, Daniel Snaddon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4 €</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Ec mat Hellé</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avatar De cendres et de feu</t>
+          <t>Coutures</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -948,22 +984,18 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>James Cameron</t>
+          <t>Alice Winocour</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Famille - 2D</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -973,28 +1005,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>En garde</t>
+          <t>Pédale rurale</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nelicia Low</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Grand Prix du Jury La Roche sur Yon - Meilleur réalisation Karlovy Vary</t>
-        </is>
-      </c>
+          <t>Antine Vasquez</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Documentaire Découverte</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1003,7 +1031,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1013,7 +1041,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Le gâteau du président</t>
+          <t>Little trouble girls</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1021,20 +1049,16 @@
           <t>VO</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CM2</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hasan Hadi</t>
+          <t>Urška Djukić</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1043,79 +1067,79 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Les toutes petites créatures 2</t>
+          <t>Marty Supreme</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lucy Izzard</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Josh Safdie</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Golden Globe meilleur acteur</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nuages flottants</t>
+          <t>Esprit(s) rebelle(s)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mikio Naruse</t>
+          <t>Natalia Chernysheva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ciné Patrimoine du samedi 18h</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Adhérents 4 € - Autres 5 €</t>
+          <t>Tarif Unique 3 €</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1123,57 +1147,61 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palestine 36</t>
+          <t>Une balle dans la tête</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Annemarie Jacir</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Grand Prix Tokyo - Meilleur film Milan</t>
-        </is>
-      </c>
+          <t>John Woo</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>Ciné Patrimoine du samedi 18h</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Partenariat Empreinte Carbonne</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Le chant des forêts</t>
+          <t>Le rêve américain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1184,36 +1212,28 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vincent Munier</t>
+          <t>Anthony Marciano</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Documentaire Famille</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4,50 €</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gourou</t>
+          <t>Le chant des forêts</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1224,18 +1244,26 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yann Gozlan</t>
+          <t>Vincent Munier</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Documentaire Coup de coeur</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Séance sup suite séance annulée</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1245,7 +1273,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Les légendaires</t>
+          <t>Les enfants de la Résistance</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1256,13 +1284,13 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guillaume Ivernel</t>
+          <t>Christophe Barratier</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Famille, Jeune Public</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1271,17 +1299,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Soulèvements</t>
+          <t>Chers parents</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1292,68 +1320,68 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomas Lacoste</t>
+          <t>Emmanuel Patron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Documentaire</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Les dimanches</t>
+          <t>Les enfants de la Résistance</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alauda Ruíz de Azúa</t>
+          <t>Christophe Barratier</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3,50 €</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Les toutes petites créatures 2</t>
+          <t>Victor comme tout le monde</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1364,26 +1392,18 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lucy Izzard</t>
+          <t>Pascal Bonitzer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1393,7 +1413,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nurenberg</t>
+          <t>La gifle</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1404,7 +1424,7 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>James Vanderbilt</t>
+          <t>Frédéric Hambalek</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1419,159 +1439,151 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Marsupilami JP famille</t>
+          <t>Ce qu'il reste de nous</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Philippe Lacheau</t>
+          <t>Cherien Dabis</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Séance EPHAD HANDI - Famille</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Tarif Unique 5 €</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Aucun autre choix</t>
+          <t>Le rêve américain</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Park Chan-Wook</t>
+          <t>Anthony Marciano</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Séance EPHAD HANDI</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Tarif Unique 5 €</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Biscuit le chien fantastique</t>
+          <t>Un monde fragile et merveilleux</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shea Wageman</t>
+          <t>Cyril Aris</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Ciné goûter, Jeune Public</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4,50 €</t>
-        </is>
-      </c>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hamnet</t>
+          <t>Jumpers</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chloé Zhao</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Meilleure film dramatique et meilleure actrice Golden Globes 2026</t>
-        </is>
-      </c>
+          <t>Daniel Chong</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Ciné Jeunes du samedi 18h</t>
+          <t>Ciné goûter, Jeune Public</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Adhérents 4 € - Autres 5 €</t>
+          <t>Tarif Unique 4,50 €</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -1579,49 +1591,57 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>A pied d'œuvre</t>
+          <t>Christy</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Valérie Donzelli</t>
+          <t>David Michôd</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ciné Jeunes du samedi 18h</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Les légendaires</t>
+          <t>La maison des femmes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1632,32 +1652,28 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guillaume Ivernel</t>
+          <t>Melisa Godet</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Promis le ciel</t>
+          <t>Allah n'est pas obligé</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1668,13 +1684,13 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erige Sehiri</t>
+          <t>Zaven Najjar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Famille à partir de 9/10 ans, Jeune Public</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -1683,17 +1699,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gourou</t>
+          <t>La guerre des prix</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1704,7 +1720,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yann Gozlan</t>
+          <t>Anthony Dechaux</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -1715,7 +1731,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1725,83 +1741,71 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Les voyages de Tereza</t>
+          <t>Alter ego</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gabriel Mascaro</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Cinélatino</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
+          <t>Nicolas Charlet, Bruno Lavaine</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dreams</t>
+          <t>Le rêve américain</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Michel Franco</t>
+          <t>Anthony Marciano</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lol 2.0</t>
+          <t>Les figures de l'ombre</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1812,45 +1816,57 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lisa Azuelos</t>
+          <t>Theodore Melfi</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4 €</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Collège Abbal</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Super Charlie</t>
+          <t>Woman and child</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jon Holmberg</t>
+          <t>Saeed Roustaee</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -1859,17 +1875,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Abel</t>
+          <t>Pillion</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1880,40 +1896,32 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Elzat Eskendir</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Grand Prix et Prix de la critique Vesoul 2025</t>
-        </is>
-      </c>
+          <t>Harry Lighton</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Ciné discussion - Coup ce cœur</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Adhérents 4 € - Autres 5 €</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Maigret et le mort amoureux</t>
+          <t>Le chant de la mer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1924,129 +1932,405 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pascal Bonitzer</t>
+          <t>Tomm Moore</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4 €</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Hellé élem</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tafiti</t>
+          <t>Love on trial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nina Wels</t>
+          <t>Kôji Fukada</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4,50 €</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Les enfants de la Résistance</t>
+          <t>Il maestro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Christophe Barratier</t>
+          <t>Andrea di Stefano</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Famille, Jeune Public</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Le mystérieux regard du flamant rose</t>
+          <t>Scarlet et l'éternité</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Diego Cespedes</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Cinélatino</t>
-        </is>
-      </c>
+          <t>Mamoru Hosoda</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
+          <t>ados à partir de 9/10 ans Sony, Jeune Public</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sony</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>La grazia</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Paolo Sorrentino</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Ciné Discussion du samedi 18h</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Le son des souvenirs</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VO</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Oliver Hermanus</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>Coup de cœur</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Planètes</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Momoko Seto</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Famille, Jeune Public</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Tarif Unique 4,50 €</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Le crime du 3e étage</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rémi Bezançon</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Léo la fabuleuse histoire de Léonard de Vinci</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Jim Capobianco</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3,80 €</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Ec Lautignac</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Léo la fabuleuse histoire de Léonard de Vinci</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Jim Capobianco</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3,80 €</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Ec Rieux</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Les filles du ciel</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bérangère Mc Neese</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outils/work/normalized.xlsx
+++ b/outils/work/normalized.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Urchin</t>
+          <t>Yellow letters</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -504,17 +504,13 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harris Dickinson</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Grand Prix Jury de jeunes Carbonne fait son cinéma - Meilleure interprétation Un certain regard Cannes</t>
-        </is>
-      </c>
+          <t>Ilker Catak</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -523,17 +519,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Le sommet des dieux</t>
+          <t>Dilili à Paris</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -542,122 +538,110 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Michel Ocelot</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2,80 €</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Patrick Imbert / Collège Noé</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rue Malaga</t>
+          <t>Angelo dans la forêt mystérieuse</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maryam Touzani</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Prix du public Venise</t>
-        </is>
-      </c>
+          <t>Vincent Paronnaud</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Tarif Unique 4 €</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Microcosmos</t>
+          <t>Silent friend</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Claude Nuridsany, Marie Pérennou</t>
+          <t>Ildiko Enyedi</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2,80 €</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Ec Labsstide Clermont</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alter ego</t>
+          <t>Arco</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -668,116 +652,108 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nicolas Charlet, Bruno Lavaine</t>
+          <t>Ugo Bienvenu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Séance EPHAD HANDI</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Tarif Unique 5 €</t>
-        </is>
-      </c>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>La couleuvre noire</t>
+          <t>Chers parents</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aurélien Vernhes-Lermusiaux</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Prix Fondation Gan</t>
-        </is>
-      </c>
+          <t>Emmanuel Patron</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Cinélatino Avant-première</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Séance EPHAD HANDI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Tarif Unique 5 €</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L'ourse et l'oiseau</t>
+          <t>La grazia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marie Caudry, Aurore Peuffier, Nina Bisyarina</t>
+          <t>Paolo Sorrentino</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>La princesse, l'ogre et la fourmi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -788,80 +764,76 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Edouard Bergeon</t>
+          <t>Eduard Nazarov</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Ciné Documentaire du samedi 18h</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>invité Jérôme Bayle attente de réponse</t>
-        </is>
-      </c>
+          <t>Tarif Unique 3 €</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Marty Supreme</t>
+          <t>Scarlet et l'éternité</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Josh Safdie</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Golden Globe meilleur acteur</t>
-        </is>
-      </c>
+          <t>Mamoru Hosoda</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Ciné Jeunes du samedi 18h - Ados, Jeune Public</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Marsupilami</t>
+          <t>Les rayons et les ombres</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -872,13 +844,13 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Philippe Lacheau</t>
+          <t>Xavier Giannoli</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Famille, Jeune Public</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -887,17 +859,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Maigret et le mort amoureux</t>
+          <t>Jumpers</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -908,28 +880,32 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pascal Bonitzer</t>
+          <t>Daniel Chong</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Les Tourouges et les Toubleus</t>
+          <t>Derrière les palmiers</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -940,30 +916,22 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Samantha Cutler, Daniel Snaddon</t>
+          <t>Meryem Benm'Barek</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4 €</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Ec mat Hellé</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -973,7 +941,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Coutures</t>
+          <t>La danse des renards</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -981,31 +949,43 @@
           <t>VF</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CM1</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alice Winocour</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+          <t>Valéry Carnoy</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Mention Jury  deJeunes Carbonne fait son Cinéma</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Découverte</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pédale rurale</t>
+          <t>Goat- Rêver plus haut</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1016,13 +996,13 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Antine Vasquez</t>
+          <t>Tyree Dillihay</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Documentaire Découverte</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1031,7 +1011,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1041,7 +1021,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Little trouble girls</t>
+          <t>Un jour avec mon père</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1052,13 +1032,17 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Urška Djukić</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Akinola Davies</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Meilleur scénario Jury de jeunes et meilleur scénario jury d'adultes FCFC Mention Caméra d'or Cannes 2025</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1067,38 +1051,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Marty Supreme</t>
+          <t>Scarlet et l'éternité</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Josh Safdie</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Golden Globe meilleur acteur</t>
-        </is>
-      </c>
+          <t>Mamoru Hosoda</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Ados à partir cde 9/10 ans, Jeune Public</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1107,101 +1087,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Esprit(s) rebelle(s)</t>
+          <t>Plus fort que moi</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Natalia Chernysheva</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Kirk Jones</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Prix montage et interpréation FCFC</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Une balle dans la tête</t>
+          <t>La femme de</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CM2</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>John Woo</t>
+          <t>David Roux</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Ciné Patrimoine du samedi 18h</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Partenariat Empreinte Carbonne</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Le rêve américain</t>
+          <t>Edmond et Lucy La forêt c'est l'aventure</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1212,68 +1184,76 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anthony Marciano</t>
+          <t>François Narboux</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Tarif Unique 3 €</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Le chant des forêts</t>
+          <t>Orwell : 2+2=5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vincent Munier</t>
+          <t>Raoul Peck</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Documentaire Coup de coeur</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Séance sup suite séance annulée</t>
-        </is>
-      </c>
+          <t>Ciné Documentaire du samedi 18h</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Les enfants de la Résistance</t>
+          <t>Projet dernière chance</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1284,32 +1264,28 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Christophe Barratier</t>
+          <t>Phil Lord, Christopher Miller</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Famille, Jeune Public</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chers parents</t>
+          <t>Les contes du pommier</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1320,28 +1296,32 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Emmanuel Patron</t>
+          <t>Patrick Pass Jr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Les enfants de la Résistance</t>
+          <t>Ceux qui comptent</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1352,36 +1332,28 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Christophe Barratier</t>
+          <t>Jean-Baptiste Léonetti</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3,50 €</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Victor comme tout le monde</t>
+          <t>Jumpers</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1392,18 +1364,22 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pascal Bonitzer</t>
+          <t>Daniel Chong</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1413,7 +1389,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>La gifle</t>
+          <t>Romeria</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1424,7 +1400,7 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Frédéric Hambalek</t>
+          <t>Carla Simon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1439,7 +1415,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1449,43 +1425,39 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ce qu'il reste de nous</t>
+          <t>Sauvage</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cherien Dabis</t>
+          <t>Camille Ponsin</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Le rêve américain</t>
+          <t>Super Mario Galaxy Le film</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1496,26 +1468,22 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anthony Marciano</t>
+          <t>Aaron Horvath</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Séance EPHAD HANDI</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Tarif Unique 5 €</t>
-        </is>
-      </c>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1525,24 +1493,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Un monde fragile et merveilleux</t>
+          <t>Une fille en or</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CM3</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cyril Aris</t>
+          <t>Jean-Luc Gaget</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1551,17 +1523,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jumpers</t>
+          <t>Le secret du loup d'Ethiopie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1572,18 +1544,18 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Daniel Chong</t>
+          <t>Baptiste Deturche</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Ciné goûter, Jeune Public</t>
+          <t>Séance EPHAD HANDI Famille, Jeune Public</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tarif Unique 4,50 €</t>
+          <t>Tarif Unique 5 €</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -1591,57 +1563,53 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Christy</t>
+          <t>Police flash 80</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>David Michôd</t>
+          <t>Jezan-Baptiste Saurel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Ciné Jeunes du samedi 18h</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>avec Empreinte Carbonne</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>La maison des femmes</t>
+          <t>Walter lapin</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1652,64 +1620,80 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Melisa Godet</t>
+          <t>Caroline Origer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Ciné goûter, Jeune Public</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Tarif Unique 4,50 €</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Allah n'est pas obligé</t>
+          <t>La soif du mal</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zaven Najjar</t>
+          <t>Orson Welles</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Famille à partir de 9/10 ans, Jeune Public</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>Ciné Patrimoine du samedi 18h</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>avec Empreinte Carbonne</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>La guerre des prix</t>
+          <t>Morlaix</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1720,7 +1704,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anthony Dechaux</t>
+          <t>Jaime Rosales</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -1731,17 +1715,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alter ego</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1752,28 +1736,32 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nicolas Charlet, Bruno Lavaine</t>
+          <t>Edouard Bergeon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Documentaire</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Le rêve américain</t>
+          <t>Les rayons et les ombres</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1784,28 +1772,32 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anthony Marciano</t>
+          <t>Xavier Giannoli</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Les figures de l'ombre</t>
+          <t>Les enfants de la Résistance</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1816,7 +1808,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Theodore Melfi</t>
+          <t>Christophe Barratier</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -1827,55 +1819,55 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4 €</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Collège Abbal</t>
-        </is>
-      </c>
+          <t>Tarif Unique 3,50 €</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Woman and child</t>
+          <t>Petites casseroles</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Saeed Roustaee</t>
+          <t>Uzi Geffenblad</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Tarif Unique 2,80 €</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1885,7 +1877,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pillion</t>
+          <t>Une jeunesse indienne Homebound</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1896,13 +1888,17 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harry Lighton</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Neeraj Ghaywan</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Grand prix jury de jeunes Festival muret</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -1911,87 +1907,79 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Le chant de la mer</t>
+          <t>À voix basse</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tomm Moore</t>
+          <t>Leyla Bouzid</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4 €</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Hellé élem</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Love on trial</t>
+          <t>Le peuple loup</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Kôji Fukada</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Tarif Unique 2,80 €</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2001,18 +1989,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Il maestro</t>
+          <t>La poupée</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>CM4</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Andrea di Stefano</t>
+          <t>Sophie Beaulieu</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2023,7 +2015,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2033,7 +2025,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scarlet et l'éternité</t>
+          <t>L'enfant du désert</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2044,26 +2036,22 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mamoru Hosoda</t>
+          <t>Gilles de Maistre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ados à partir de 9/10 ans Sony, Jeune Public</t>
+          <t>Famille, Jeune Public</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Sony</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2073,64 +2061,56 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>La grazia</t>
+          <t>Compostelle</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paolo Sorrentino</t>
+          <t>Yann Samuell</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Ciné Discussion du samedi 18h</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Le son des souvenirs</t>
+          <t>Le dernier pour la route</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oliver Hermanus</t>
+          <t>Frnacesco Sossai</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2139,39 +2119,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Planètes</t>
+          <t>A walk to freedom</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Momoko Seto</t>
+          <t>Justin Chadwick</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Famille, Jeune Public</t>
+          <t>Scolaire</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Tarif Unique 4,50 €</t>
+          <t>Tarif Unique 4 €</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -2179,17 +2159,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Le crime du 3e étage</t>
+          <t>Les vacances de Monsieur Hulot</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2200,137 +2180,61 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rémi Bezançon</t>
+          <t>Jacques Tati</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Tarif Unique 2,80 €</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Léo la fabuleuse histoire de Léonard de Vinci</t>
+          <t>La corde au cou</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jim Capobianco</t>
+          <t>Gus Van Sant</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3,80 €</t>
-        </is>
-      </c>
+          <t>Coup de coeur</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Ec Lautignac</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Léo la fabuleuse histoire de Léonard de Vinci</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Jim Capobianco</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3,80 €</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Ec Rieux</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Les filles du ciel</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Bérangère Mc Neese</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>avec Empreinte Carbonne</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outils/work/normalized.xlsx
+++ b/outils/work/normalized.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>courts_metrages</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Realisateur</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recompenses</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Categorie</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Tarif</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
@@ -502,19 +507,20 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Ilker Catak</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -538,19 +544,20 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Michel Ocelot</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -574,23 +581,24 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Vincent Paronnaud</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Tarif Unique 4 €</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -614,19 +622,20 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Ildiko Enyedi</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -650,19 +659,20 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Ugo Bienvenu</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -686,23 +696,24 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Emmanuel Patron</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Séance EPHAD HANDI</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Tarif Unique 5 €</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -726,19 +737,20 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Paolo Sorrentino</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -762,23 +774,24 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Eduard Nazarov</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Tarif Unique 3 €</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -802,23 +815,24 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Mamoru Hosoda</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Ciné Jeunes du samedi 18h - Ados, Jeune Public</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Adhérent 4 € - Autres 5 €</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -842,19 +856,20 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Xavier Giannoli</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Coup de cœur</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -878,19 +893,20 @@
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Daniel Chong</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -914,19 +930,20 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Meryem Benm'Barek</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -956,21 +973,26 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>[{"code": "CM1", "titre": "Je ne suis pas", "genre": "Film militant", "duree": "04'00", "texte": "Je ne suis pas - Film militant - 04'00"}]</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>Valéry Carnoy</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Mention Jury  deJeunes Carbonne fait son Cinéma</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -994,19 +1016,20 @@
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>Tyree Dillihay</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1030,23 +1053,24 @@
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>Akinola Davies</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Meilleur scénario Jury de jeunes et meilleur scénario jury d'adultes FCFC Mention Caméra d'or Cannes 2025</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Coup de cœur</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1070,19 +1094,20 @@
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Mamoru Hosoda</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Ados à partir cde 9/10 ans, Jeune Public</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1106,23 +1131,24 @@
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Kirk Jones</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Prix montage et interpréation FCFC</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1152,13 +1178,18 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>[{"code": "CM2", "titre": "Le futur sera chauve", "genre": "Animation", "duree": "05'36", "texte": "Le futur sera chauve - Animation - 05'36"}]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>David Roux</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1182,23 +1213,24 @@
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>François Narboux</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Tarif Unique 3 €</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1222,23 +1254,24 @@
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Raoul Peck</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Ciné Documentaire du samedi 18h</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Adhérent 4 € - Autres 5 €</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1262,15 +1295,16 @@
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>Phil Lord, Christopher Miller</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1294,19 +1328,20 @@
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>Patrick Pass Jr</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1330,15 +1365,16 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>Jean-Baptiste Léonetti</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1362,19 +1398,20 @@
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>Daniel Chong</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1398,19 +1435,20 @@
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>Carla Simon</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1434,15 +1472,16 @@
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>Camille Ponsin</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1466,19 +1505,20 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>Aaron Horvath</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1508,17 +1548,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>[{"code": "CM3", "titre": "Super V", "genre": "Comédie", "duree": "02'00", "texte": "Super V - Comédie - 02'00"}]</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>Jean-Luc Gaget</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1542,23 +1587,24 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Baptiste Deturche</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
         <is>
           <t>Séance EPHAD HANDI Famille, Jeune Public</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Tarif Unique 5 €</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1582,15 +1628,16 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>Jezan-Baptiste Saurel</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
         <is>
           <t>avec Empreinte Carbonne</t>
         </is>
@@ -1618,23 +1665,24 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>Caroline Origer</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
         <is>
           <t>Ciné goûter, Jeune Public</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Tarif Unique 4,50 €</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1658,23 +1706,24 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
         <is>
           <t>Orson Welles</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
         <is>
           <t>Ciné Patrimoine du samedi 18h</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Adhérent 4 € - Autres 5 €</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>avec Empreinte Carbonne</t>
         </is>
@@ -1702,15 +1751,16 @@
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>Jaime Rosales</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1734,19 +1784,20 @@
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>Edouard Bergeon</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
         <is>
           <t>Documentaire</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1770,19 +1821,20 @@
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>Xavier Giannoli</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
         <is>
           <t>Coup de cœur</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1806,23 +1858,24 @@
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>Christophe Barratier</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Tarif Unique 3,50 €</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1846,23 +1899,24 @@
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>Uzi Geffenblad</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Tarif Unique 2,80 €</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1886,23 +1940,24 @@
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
         <is>
           <t>Neeraj Ghaywan</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Grand prix jury de jeunes Festival muret</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Coup de cœur</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1926,19 +1981,20 @@
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>Leyla Bouzid</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1964,17 +2020,18 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Tarif Unique 2,80 €</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2004,13 +2061,18 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>[{"code": "CM4", "titre": "Des filles et des chiens", "genre": "Comédie", "duree": "05'00", "texte": "Des filles et des chiens - Comédie - 05'00"}]</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>Sophie Beaulieu</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2034,19 +2096,20 @@
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
         <is>
           <t>Gilles de Maistre</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
         <is>
           <t>Famille, Jeune Public</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2070,15 +2133,16 @@
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
         <is>
           <t>Yann Samuell</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2102,19 +2166,20 @@
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
         <is>
           <t>Frnacesco Sossai</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2138,23 +2203,24 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
         <is>
           <t>Justin Chadwick</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Tarif Unique 4 €</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2178,23 +2244,24 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
         <is>
           <t>Jacques Tati</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Tarif Unique 2,80 €</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2218,19 +2285,20 @@
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
         <is>
           <t>Gus Van Sant</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
         <is>
           <t>Coup de coeur</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
         <is>
           <t>avec Empreinte Carbonne</t>
         </is>

--- a/outils/work/normalized.xlsx
+++ b/outils/work/normalized.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,61 +413,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Heure</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Titre</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>courts_metrages</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Realisateur</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Recompenses</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Categorie</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Tarif</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
@@ -488,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,7 +486,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yellow letters</t>
+          <t>Sukkwan island</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -510,7 +498,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ilker Catak</t>
+          <t>Vladimir de Fontenay</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -525,35 +513,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dilili à Paris</t>
+          <t>La fille du Kombini</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>VO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CM3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[{"code": "CM3", "titre": "Super V", "genre": "Comédie", "duree": "02'00", "texte": "Super V - Comédie - 02'00"}]</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Michel Ocelot</t>
+          <t>Yûho Ishibashi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Scolaire</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -562,17 +558,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Angelo dans la forêt mystérieuse</t>
+          <t>Nous l'orchestre</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -584,110 +580,114 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vincent Paronnaud</t>
+          <t>Philippe Béziat</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4 €</t>
-        </is>
-      </c>
+          <t>Coup de cœur Documentaire</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Silent friend</t>
+          <t>Jeune pousse</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ildiko Enyedi</t>
+          <t>Anastasia Sokolova</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Tarif Unique 3 €</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arco</t>
+          <t>Good luck have fun don't die</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ugo Bienvenu</t>
+          <t>Gore Verbinski</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>Ciné Jeunes du samedi 18h - Ados, Jeune Public</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chers parents</t>
+          <t>Mauvaise pioche</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -699,54 +699,46 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emmanuel Patron</t>
+          <t>G Jugnot</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Séance EPHAD HANDI</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Tarif Unique 5 €</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>La grazia</t>
+          <t>L'odyssée de Céleste</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Paolo Sorrentino</t>
+          <t>Kid Koala</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -755,17 +747,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>La princesse, l'ogre et la fourmi</t>
+          <t>Juste une illusion</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -777,36 +769,28 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eduard Nazarov</t>
+          <t>Olivier Nakache, Eric Toledano</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Scarlet et l'éternité</t>
+          <t>Au fil de l'eau</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -818,48 +802,52 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mamoru Hosoda</t>
+          <t>Diek Grobler</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Ciné Jeunes du samedi 18h - Ados, Jeune Public</t>
+          <t>Scolaire</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>3 €</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Ec mat Chanfreau</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Les rayons et les ombres</t>
+          <t>Sorda</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Xavier Giannoli</t>
+          <t>Eva Libertad Garcia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -874,54 +862,58 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jumpers</t>
+          <t>La corde au cou</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daniel Chong</t>
+          <t>Gus Van Sant</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Partenariat Empreinte Carbonne</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Derrière les palmiers</t>
+          <t>Mi amor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -933,7 +925,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meryem Benm'Barek</t>
+          <t>Guillaume Nicloux</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -943,22 +935,26 @@
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Partenariat Empreinte Carbonne</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>La danse des renards</t>
+          <t>Compostelle</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -966,29 +962,17 @@
           <t>VF</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CM1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>[{"code": "CM1", "titre": "Je ne suis pas", "genre": "Film militant", "duree": "04'00", "texte": "Je ne suis pas - Film militant - 04'00"}]</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Valéry Carnoy</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Mention Jury  deJeunes Carbonne fait son Cinéma</t>
-        </is>
-      </c>
+          <t>Yann Samuell</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Séance EPHAD HANDI</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -997,35 +981,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Goat- Rêver plus haut</t>
+          <t>Mon grand frère et moi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>VO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CM4</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[{"code": "CM4", "titre": "Des filles et des chiens", "genre": "Comédie", "duree": "05'00", "texte": "Des filles et des chiens - Comédie - 05'00"}]</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tyree Dillihay</t>
+          <t>Ryôta Nakano</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1034,39 +1026,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Un jour avec mon père</t>
+          <t>Super Mario Galaxy Le film</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Akinola Davies</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Meilleur scénario Jury de jeunes et meilleur scénario jury d'adultes FCFC Mention Caméra d'or Cannes 2025</t>
-        </is>
-      </c>
+          <t>Aaron Horvarth</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1075,44 +1063,48 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scarlet et l'éternité</t>
+          <t>Nuestra tierra</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mamoru Hosoda</t>
+          <t>Lucrecia Martel</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ados à partir cde 9/10 ans, Jeune Public</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>Ciné Documentaire du samedi 18h</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1122,7 +1114,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plus fort que moi</t>
+          <t>Michaël</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1134,36 +1126,28 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kirk Jones</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Prix montage et interpréation FCFC</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+          <t>Antoine Fuqua</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>La femme de</t>
+          <t>Le secret du loup d'Ethiopie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1171,40 +1155,36 @@
           <t>VF</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CM2</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[{"code": "CM2", "titre": "Le futur sera chauve", "genre": "Animation", "duree": "05'36", "texte": "Le futur sera chauve - Animation - 05'36"}]</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>David Roux</t>
+          <t>Baptiste Deturche</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Famille TU 4, 50 €, Jeune Public</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Edmond et Lucy La forêt c'est l'aventure</t>
+          <t>C'est quoi l'amour ?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1216,36 +1196,28 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>François Narboux</t>
+          <t>Fabien Gorgeart</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Orwell : 2+2=5</t>
+          <t>Le cri des gardes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1257,36 +1229,32 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Raoul Peck</t>
+          <t>Claire Denis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Ciné Documentaire du samedi 18h</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Projet dernière chance</t>
+          <t>L'enfant du désert</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1298,28 +1266,32 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phil Lord, Christopher Miller</t>
+          <t>Gilles de Maistre</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Famille, Jeune Public</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Les contes du pommier</t>
+          <t>MacPat le chat chanteur</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1331,32 +1303,40 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Patrick Pass Jr</t>
+          <t>Nils Skapans</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3 €</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Ec Saint julien</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ceux qui comptent</t>
+          <t>Dans la roue du petit Prince</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1368,46 +1348,58 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Jean-Baptiste Léonetti</t>
+          <t>Yannick Billard</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>film récupéré par Ciné Carbonne EEPU Chanfreau</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jumpers</t>
+          <t>Projet dernière chance</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daniel Chong</t>
+          <t>Phil Lord</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -1416,44 +1408,44 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romeria</t>
+          <t>Conférence filmée Serge Tisseron</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Carla Simon</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>suivi d'un échange avec G Biarc psychologue et FCPE / Prtenariat FCPE Semaine moins d'écrans</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1463,58 +1455,62 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sauvage</t>
+          <t>The world of love</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Camille Ponsin</t>
+          <t>Ga Eun Yoon</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Découverte</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Super Mario Galaxy Le film</t>
+          <t>Soumsoum la nuit des astres</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Aaron Horvath</t>
+          <t>Mahamat-Saleh Aroun</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1523,17 +1519,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Une fille en or</t>
+          <t>Bily Elliot</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1541,44 +1537,44 @@
           <t>VF</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>CM3</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>[{"code": "CM3", "titre": "Super V", "genre": "Comédie", "duree": "02'00", "texte": "Super V - Comédie - 02'00"}]</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Jean-Luc Gaget</t>
+          <t>Stephen Daldry</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Filmo 3,50 €</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Ec élem Chanfreau</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Le secret du loup d'Ethiopie</t>
+          <t>Juste une illusion</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1590,36 +1586,28 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Baptiste Deturche</t>
+          <t>Olivier Nakache, Eric Toledano</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Séance EPHAD HANDI Famille, Jeune Public</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Tarif Unique 5 €</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Police flash 80</t>
+          <t>Elfie et les supers Elfkins</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1631,32 +1619,36 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Jezan-Baptiste Saurel</t>
+          <t>Ute von Munchow-Pohl</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>avec Empreinte Carbonne</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Tarif Unique 4,50 €</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Walter lapin</t>
+          <t>Pour le meilleur</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1668,132 +1660,116 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Caroline Origer</t>
+          <t>Marie-Castille Mention-Schaar</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Ciné goûter, Jeune Public</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4,50 €</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>La soif du mal</t>
+          <t>Elise sous emprise</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Orson Welles</t>
+          <t>Marie Rémond</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Ciné Patrimoine du samedi 18h</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>avec Empreinte Carbonne</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morlaix</t>
+          <t>Hayat</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jaime Rosales</t>
+          <t>Zeki Demurkubuz</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Romeria</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Edouard Bergeon</t>
+          <t>Carla Simon</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -1802,35 +1778,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Les rayons et les ombres</t>
+          <t>Cocotte</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>VO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CM5</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>[{"code": "CM5", "titre": "Poisson rouge", "genre": "Fiction", "duree": "03'00", "texte": "Poisson rouge - Fiction - 03'00"}]</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Xavier Giannoli</t>
+          <t>György Palfi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -1839,17 +1823,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Les enfants de la Résistance</t>
+          <t>La vénus électrique</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1861,36 +1845,36 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Christophe Barratier</t>
+          <t>Pierre Salvadori</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3,50 €</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ouverture Cannes 2026</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Petites casseroles</t>
+          <t>L'odyssée de Céleste JP</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1902,18 +1886,18 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Uzi Geffenblad</t>
+          <t>Kid Koala</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Scolaire</t>
+          <t>Ciné goûter, Jeune Public</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Tarif Unique 2,80 €</t>
+          <t>Tarif Unique 4,50 €</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -1921,17 +1905,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Une jeunesse indienne Homebound</t>
+          <t>Vol au-dessus d'un nid de coucou</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1943,26 +1927,26 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neeraj Ghaywan</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Grand prix jury de jeunes Festival muret</t>
-        </is>
-      </c>
+          <t>Milos Forman</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>Ciné Club du samedi 18h</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1972,44 +1956,40 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>À voix basse</t>
+          <t>Le diable s'habille en Prada 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leyla Bouzid</t>
+          <t>David Frankel</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Le peuple loup</t>
+          <t>ChaO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2019,34 +1999,34 @@
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Yasuhiro Aoki</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Tarif Unique 2,80 €</t>
-        </is>
-      </c>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>La poupée</t>
+          <t>La vénus électrique</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2054,40 +2034,40 @@
           <t>VF</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>CM4</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>[{"code": "CM4", "titre": "Des filles et des chiens", "genre": "Comédie", "duree": "05'00", "texte": "Des filles et des chiens - Comédie - 05'00"}]</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sophie Beaulieu</t>
+          <t>Pierre Salvadori</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Ouverture Cannes 2026</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>L'enfant du désert</t>
+          <t>Contes sur moi</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2099,32 +2079,40 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gilles de Maistre</t>
+          <t>Mohammad Ali Soleymanzadeh</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Famille, Jeune Public</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4 €</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Ec Hellé</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Compostelle</t>
+          <t>Le roi des masques</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2136,40 +2124,52 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Yann Samuell</t>
+          <t>Wu Tian-Ming</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2,80 €</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Lautignac</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Le dernier pour la route</t>
+          <t>Vivaldi et moi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Frnacesco Sossai</t>
+          <t>Damiano Michieletto</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2180,129 +2180,6 @@
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>A walk to freedom</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Justin Chadwick</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4 €</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Les vacances de Monsieur Hulot</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Jacques Tati</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Tarif Unique 2,80 €</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>La corde au cou</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Gus Van Sant</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Coup de coeur</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>avec Empreinte Carbonne</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outils/work/normalized.xlsx
+++ b/outils/work/normalized.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,61 +425,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Heure</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Titre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>courts_metrages</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Realisateur</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recompenses</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Categorie</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Tarif</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
@@ -476,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,7 +498,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sukkwan island</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,22 +510,22 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vladimir de Fontenay</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+          <t>Tereza Nvotova</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Prix Sang neuf Reims Polar 2026</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,52 +535,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>La fille du Kombini</t>
+          <t>L'abandon</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CM3</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[{"code": "CM3", "titre": "Super V", "genre": "Comédie", "duree": "02'00", "texte": "Super V - Comédie - 02'00"}]</t>
-        </is>
-      </c>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yûho Ishibashi</t>
+          <t>Vincent Garenq</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Cannes 2026 Hors compétition</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nous l'orchestre</t>
+          <t>Minuscule</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -578,34 +582,34 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Philippe Béziat</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Coup de cœur Documentaire</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Filmo 3,50 €</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jeune pousse</t>
+          <t>Zootopia 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -615,20 +619,16 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Anastasia Sokolova</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Scolaire</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Tarif Unique 3 €</t>
+          <t>Filmo 3,50 €</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -636,58 +636,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Good luck have fun don't die</t>
+          <t>L'être aimé</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gore Verbinski</t>
+          <t>Rodrigo Sorogoyen</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Ciné Jeunes du samedi 18h - Ados, Jeune Public</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Cannes 2026 Compétition</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mauvaise pioche</t>
+          <t>L'odyssée de Céleste</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -699,28 +695,32 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>G Jugnot</t>
+          <t>Kid Koala</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L'odyssée de Céleste</t>
+          <t>Histoires parralèles</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -732,32 +732,32 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kid Koala</t>
+          <t>Asghar Farhadi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Cannes 2026 Compétition</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Juste une illusion</t>
+          <t>Tout va super</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -769,7 +769,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Olivier Nakache, Eric Toledano</t>
+          <t>Patrick Cassir</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -780,52 +780,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Au fil de l'eau</t>
+          <t>The new west</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Diek Grobler</t>
+          <t>Kate Beecroft</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>3 €</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Ec mat Chanfreau</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -835,34 +823,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sorda</t>
+          <t>L'affaire Zanetti</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eva Libertad Garcia</t>
+          <t>Leonardo Di Costanzo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -872,48 +856,44 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>La corde au cou</t>
+          <t>Histoires parralèles</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gus Van Sant</t>
+          <t>Asghar Farhadi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Partenariat Empreinte Carbonne</t>
+          <t>Cannes 2026 Compétition</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mi amor</t>
+          <t>Tout en haut du monde</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -925,26 +905,26 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Guillaume Nicloux</t>
+          <t>Rémi Chayé</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Partenariat Empreinte Carbonne</t>
-        </is>
-      </c>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Filmo 3,50 €</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -954,7 +934,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Compostelle</t>
+          <t>Pour le plaisir</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -966,7 +946,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yann Samuell</t>
+          <t>Reem Kherici</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -975,13 +955,17 @@
           <t>Séance EPHAD HANDI</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Tarif Unique 5 €</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -991,7 +975,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mon grand frère et moi</t>
+          <t>Le garçon qui faisait danser les collines</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -999,44 +983,36 @@
           <t>VO</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CM4</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[{"code": "CM4", "titre": "Des filles et des chiens", "genre": "Comédie", "duree": "05'00", "texte": "Des filles et des chiens - Comédie - 05'00"}]</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ryôta Nakano</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+          <t>Georgi M. Unkovski</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Prix Carbonne</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Super Mario Galaxy Le film</t>
+          <t>Nouveaux copains à Puffin Rock</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1048,13 +1024,13 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Aaron Horvarth</t>
+          <t>Jeremy Purcell</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Ciné goûter, Jeune Public</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1063,7 +1039,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1073,7 +1049,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nuestra tierra</t>
+          <t>Star wars The Mandalorian and Grogu</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1085,13 +1061,13 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lucrecia Martel</t>
+          <t>Jon Favreau</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ciné Documentaire du samedi 18h</t>
+          <t>Ciné Jeunes du samedi 18h</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1104,7 +1080,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1114,19 +1090,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Michaël</t>
+          <t>L'abandon</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Antoine Fuqua</t>
+          <t>Vincent Garenq</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1137,7 +1113,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1147,7 +1123,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Le secret du loup d'Ethiopie</t>
+          <t>CHaO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1159,7 +1135,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Baptiste Deturche</t>
+          <t>Yasuhiro Aoki</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1174,7 +1150,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1184,58 +1160,58 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C'est quoi l'amour ?</t>
+          <t>Autofiction</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fabien Gorgeart</t>
+          <t>Pedro Almodovar</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Cannes 2026 Compétition</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Le cri des gardes</t>
+          <t>Rencontres vidéos scolaires</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Claire Denis</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Gratuit</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1244,17 +1220,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>L'enfant du désert</t>
+          <t>La vénus électrique</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1266,77 +1242,69 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gilles de Maistre</t>
+          <t>Pierre Salvadori</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Famille, Jeune Public</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Ouverture Cannes 2026</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MacPat le chat chanteur</t>
+          <t>L'être aimé</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nils Skapans</t>
+          <t>Rodrigo Sorogoyen</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>3 €</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Ec Saint julien</t>
+          <t>Cannes 2026 Compétition</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dans la roue du petit Prince</t>
+          <t>D'un monde à l'autre</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1348,132 +1316,124 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yannick Billard</t>
+          <t>Jérémie Renier</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>gratuit</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>film récupéré par Ciné Carbonne EEPU Chanfreau</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Projet dernière chance</t>
+          <t>C'est quoi l'amour ?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phil Lord</t>
+          <t>Fabien Gorgeart</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>Séance EPHAD HANDI</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Tarif Unique 5 €</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Conférence filmée Serge Tisseron</t>
+          <t>Colony</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sang-Ho Yeon</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>gratuit</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suivi d'un échange avec G Biarc psychologue et FCPE / Prtenariat FCPE Semaine moins d'écrans</t>
+          <t>Cannes 2026 Hors compétition</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>The world of love</t>
+          <t>Super Mario Galaxy Le film</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ga Eun Yoon</t>
+          <t>Aaron Horvath</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1482,54 +1442,54 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Soumsoum la nuit des astres</t>
+          <t>L'objet du délit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mahamat-Saleh Aroun</t>
+          <t>Agnès Jaoui</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Cannes 2026 Hors Compétition</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bily Elliot</t>
+          <t>Le vertige</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1541,30 +1501,22 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Stephen Daldry</t>
+          <t>Quentin Dupieux</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Filmo 3,50 €</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Ec élem Chanfreau</t>
+          <t>Cannes 2026 Cannes Quinzaine des cinéastes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1574,19 +1526,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Juste une illusion</t>
+          <t>The Christophers</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Olivier Nakache, Eric Toledano</t>
+          <t>Steven Soderbergh</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1597,91 +1549,91 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Elfie et les supers Elfkins</t>
+          <t>Sur la route d'Omaha</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ute von Munchow-Pohl</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4,50 €</t>
-        </is>
-      </c>
+          <t>Cole Webley</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Deauville 2025 Prix du jury</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pour le meilleur</t>
+          <t>Autofiction</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Marie-Castille Mention-Schaar</t>
+          <t>pedro almodovar</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Cannes 2026 Compétition</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Elise sous emprise</t>
+          <t>Nouveaux copains à Puffin Rock</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1693,55 +1645,63 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Marie Rémond</t>
+          <t>Cole Webley</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Tarif Unique 4,50 €</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hayat</t>
+          <t>Star wars The Mandalorian and Grogu</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Zeki Demurkubuz</t>
+          <t>Jon Favreau</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>Ciné Club ou Ciné Documentaire du samedi 18h</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1751,34 +1711,30 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romeria</t>
+          <t>La bataille de Gaulle L'âge de fer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carla Simon</t>
+          <t>Antonin Baudry</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1788,52 +1744,44 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cocotte</t>
+          <t>Ulysse</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>CM5</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>[{"code": "CM5", "titre": "Poisson rouge", "genre": "Fiction", "duree": "03'00", "texte": "Poisson rouge - Fiction - 03'00"}]</t>
-        </is>
-      </c>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>György Palfi</t>
+          <t>Laetitia Masson</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Clôture Un certain regard Cannes 2026</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>La vénus électrique</t>
+          <t>Scarlet et l'éternité</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1845,341 +1793,46 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pierre Salvadori</t>
+          <t>Mamoru Hosoda</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Ouverture Cannes 2026</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>L'odyssée de Céleste JP</t>
+          <t>L'illusion de Yakushima</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Kid Koala</t>
+          <t>Naomi Kawase</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Ciné goûter, Jeune Public</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4,50 €</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Vol au-dessus d'un nid de coucou</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Milos Forman</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Ciné Club du samedi 18h</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Le diable s'habille en Prada 2</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>David Frankel</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>ChaO</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Yasuhiro Aoki</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>La vénus électrique</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Pierre Salvadori</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Ouverture Cannes 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Contes sur moi</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Mohammad Ali Soleymanzadeh</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>4 €</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Ec Hellé</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Le roi des masques</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Wu Tian-Ming</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2,80 €</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Lautignac</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Vivaldi et moi</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Damiano Michieletto</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
